--- a/Young_Ex3A_tables.xlsx
+++ b/Young_Ex3A_tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Amaiyah Young\Documents\DATA_Labs\W2_Workshop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FF9A96E-BE49-488D-B75B-CFEAB929D9EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F93CED-CD99-4533-BA9B-FFCE6AA8F36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="10440" windowWidth="19410" windowHeight="10545" activeTab="1" xr2:uid="{C659A571-86D8-45D5-BD9B-D28A601F991A}"/>
+    <workbookView xWindow="19095" yWindow="10440" windowWidth="19410" windowHeight="10545" xr2:uid="{C659A571-86D8-45D5-BD9B-D28A601F991A}"/>
   </bookViews>
   <sheets>
     <sheet name="Owner" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>OwnerID</t>
   </si>
@@ -70,13 +70,28 @@
   </si>
   <si>
     <t xml:space="preserve"> the OwnerID would be the foreign key</t>
+  </si>
+  <si>
+    <t>365-658-999</t>
+  </si>
+  <si>
+    <t>Emily longwood</t>
+  </si>
+  <si>
+    <t>EL@gmail.com</t>
+  </si>
+  <si>
+    <t>CoCo</t>
+  </si>
+  <si>
+    <t>Labadoddle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,6 +102,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -121,19 +144,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30"/>
     <cellStyle name="20% - Accent3" xfId="2" builtinId="38"/>
+    <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -492,15 +518,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9478030D-3BD7-48B2-8DC5-26B1D41DE9DE}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" customWidth="1"/>
-    <col min="5" max="5" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="33.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -514,15 +543,32 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E7" s="1" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>15682</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F10" s="1" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{5982055D-BA90-409C-A9A1-1489190E48BD}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -535,6 +581,7 @@
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" customWidth="1"/>
     <col min="5" max="5" width="41.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -550,6 +597,20 @@
       </c>
       <c r="D1" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>15978</v>
+      </c>
+      <c r="B2">
+        <v>15682</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
